--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF72631B-0430-4054-980A-CD80D832A0A7}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7043877E-A105-466F-B8FC-6AD2D7514B58}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -285,6 +285,15 @@
   </si>
   <si>
     <t>SM141K06TF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54mm JST 3 pin </t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds</t>
+  </si>
+  <si>
+    <t>B3B-XH-A</t>
   </si>
 </sst>
 </file>
@@ -671,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
@@ -1204,34 +1213,54 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>0.13</v>
+      </c>
+      <c r="E27">
+        <v>0.13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>80</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>9</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>7.39</v>
       </c>
-      <c r="E27">
+      <c r="E28">
         <v>66.510000000000005</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F28" s="1"/>
-    </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>36</v>
       </c>
-      <c r="B29">
-        <f>SUM(E2:E27)</f>
-        <v>180.36500000000004</v>
+      <c r="B30">
+        <f>SUM(E2:E28)</f>
+        <v>180.49500000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1277,7 @@
     <hyperlink ref="F12" r:id="rId10" display="https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/bk-870/3829737" xr:uid="{27F9BEB5-8046-41B8-A401-6B801AA65292}"/>
     <hyperlink ref="F14" r:id="rId11" display="https://www.amazon.com/Gigastone-10-Pack-Surveillance-Security-Action/dp/B0876H387X/ref=asc_df_B0876H387X?mcid=a36b7487c2ef3bf38be475383d962644&amp;hvocijid=8673258576435803325-B0876H387X-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=8673258576435803325&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435181978&amp;psc=1" xr:uid="{3874B344-6752-4D37-A373-3C0F2F6D39FD}"/>
     <hyperlink ref="F16" r:id="rId12" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
-    <hyperlink ref="F17" r:id="rId13" display="https://www.digikey.com/en/products/filter/chip-resistor-surface-mount/52?s=N4IgTCBcDaIMoFkAiACASgUwM4EssBcB7AJxAF0BfIA" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
+    <hyperlink ref="F17" r:id="rId13" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
     <hyperlink ref="F18" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
     <hyperlink ref="F21" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
     <hyperlink ref="F22" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
@@ -1260,9 +1289,10 @@
     <hyperlink ref="F19" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
     <hyperlink ref="F20" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
     <hyperlink ref="F3" r:id="rId24" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F27" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F28" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F27" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId26"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7043877E-A105-466F-B8FC-6AD2D7514B58}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152FAEFB-A4BB-469B-BA28-EC4D5D003E9E}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -233,9 +233,6 @@
     <t>https://www.digikey.com/en/products/detail/c-k/JS202011CQN/1640097</t>
   </si>
   <si>
-    <t>RES SMD (100, 1k, 2K, 4.7k) OHM 1% 1/4W 1206</t>
-  </si>
-  <si>
     <t xml:space="preserve"> C1206S104K5RACAUTO 0.1 uF 10% 50V Ceramic Capacitor X7R 1206 (3216 Metric)</t>
   </si>
   <si>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>B3B-XH-A</t>
+  </si>
+  <si>
+    <t>RES SMD (1k, 2K, 4.7k) OHM 1% 1/4W 1206</t>
   </si>
 </sst>
 </file>
@@ -733,10 +733,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>2.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1053,10 +1053,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
         <v>68</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1068,15 +1068,15 @@
         <v>0.4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1088,15 +1088,15 @@
         <v>0.2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1119,13 +1119,13 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>3.58</v>
       </c>
       <c r="E22">
-        <v>7.16</v>
+        <v>3.58</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>58</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1208,15 +1208,15 @@
         <v>2.15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1228,15 +1228,15 @@
         <v>0.13</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -1248,7 +1248,7 @@
         <v>66.510000000000005</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B30">
         <f>SUM(E2:E28)</f>
-        <v>180.49500000000003</v>
+        <v>176.91500000000002</v>
       </c>
     </row>
   </sheetData>

--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152FAEFB-A4BB-469B-BA28-EC4D5D003E9E}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C7C9A8-1D10-4453-9B45-A2BEE11E1D62}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -294,6 +294,15 @@
   </si>
   <si>
     <t>RES SMD (1k, 2K, 4.7k) OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>Schottky Diode</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/onsemi/BAT54T1G/918319</t>
+  </si>
+  <si>
+    <t>BAT54T1G</t>
   </si>
 </sst>
 </file>
@@ -680,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
@@ -1053,214 +1062,234 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E19">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E20">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>1.68</v>
+        <v>0.2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>3.58</v>
+        <v>0.42</v>
       </c>
       <c r="E22">
-        <v>3.58</v>
+        <v>1.68</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>6.54</v>
+        <v>3.58</v>
       </c>
       <c r="E23">
-        <v>6.54</v>
+        <v>3.58</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>1.05</v>
+        <v>6.54</v>
       </c>
       <c r="E24">
-        <v>1.05</v>
+        <v>6.54</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="E25">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>2.15</v>
+        <v>0.91</v>
       </c>
       <c r="E26">
-        <v>2.15</v>
+        <v>0.91</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>0.13</v>
+        <v>2.15</v>
       </c>
       <c r="E27">
-        <v>0.13</v>
+        <v>2.15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0.13</v>
+      </c>
+      <c r="E28">
+        <v>0.13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>79</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>81</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>9</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <v>7.39</v>
       </c>
-      <c r="E28">
+      <c r="E29">
         <v>66.510000000000005</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F29" s="1"/>
-    </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="B30">
-        <f>SUM(E2:E28)</f>
-        <v>176.91500000000002</v>
+      <c r="B31">
+        <f>SUM(E2:E29)</f>
+        <v>177.01500000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1279,20 +1308,21 @@
     <hyperlink ref="F16" r:id="rId12" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
     <hyperlink ref="F17" r:id="rId13" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
     <hyperlink ref="F18" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
-    <hyperlink ref="F21" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
-    <hyperlink ref="F22" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="F23" r:id="rId17" display="https://www.grainger.com/product/Pipe-PVC-1ABA1" xr:uid="{98BE1843-601E-422A-8251-9162A4C6D813}"/>
-    <hyperlink ref="F24" r:id="rId18" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
-    <hyperlink ref="F25" r:id="rId19" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="F22" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
+    <hyperlink ref="F23" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
+    <hyperlink ref="F24" r:id="rId17" display="https://www.grainger.com/product/Pipe-PVC-1ABA1" xr:uid="{98BE1843-601E-422A-8251-9162A4C6D813}"/>
+    <hyperlink ref="F25" r:id="rId18" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
+    <hyperlink ref="F26" r:id="rId19" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
     <hyperlink ref="F13" r:id="rId20" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
     <hyperlink ref="F15" r:id="rId21" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="F19" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="F20" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="F20" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="F21" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
     <hyperlink ref="F3" r:id="rId24" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F28" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="F27" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F29" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F28" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F19" r:id="rId27" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId27"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C7C9A8-1D10-4453-9B45-A2BEE11E1D62}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66033065-B9D6-4C7D-A5E8-88357E117D06}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -131,9 +131,6 @@
     <t xml:space="preserve"> Schedule 40 Clear Pipe, Non-threaded</t>
   </si>
   <si>
-    <t>4" PVC pipe</t>
-  </si>
-  <si>
     <t>PRT-11864</t>
   </si>
   <si>
@@ -227,12 +224,6 @@
     <t>https://oshpark.com/</t>
   </si>
   <si>
-    <t>JS202011CQN</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/c-k/JS202011CQN/1640097</t>
-  </si>
-  <si>
     <t xml:space="preserve"> C1206S104K5RACAUTO 0.1 uF 10% 50V Ceramic Capacitor X7R 1206 (3216 Metric)</t>
   </si>
   <si>
@@ -299,10 +290,16 @@
     <t>Schottky Diode</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/onsemi/BAT54T1G/918319</t>
-  </si>
-  <si>
-    <t>BAT54T1G</t>
+    <t>https://www.digikey.com/en/products/detail/kyocera-avx/SD1206T020S1R0/3749511</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PVC pipe</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/450301014042/5209104</t>
+  </si>
+  <si>
+    <t>SD1206T020S1R0</t>
   </si>
 </sst>
 </file>
@@ -702,22 +699,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
         <v>40</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -737,15 +734,15 @@
         <v>24.9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -757,7 +754,7 @@
         <v>2.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -777,7 +774,7 @@
         <v>1.4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -797,7 +794,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -817,7 +814,7 @@
         <v>5.2450000000000001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -837,7 +834,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -857,7 +854,7 @@
         <v>12.67</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -865,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -877,7 +874,7 @@
         <v>4.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -897,7 +894,7 @@
         <v>13.5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -917,7 +914,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -937,7 +934,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -957,7 +954,7 @@
         <v>8.23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -977,27 +974,27 @@
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>63</v>
+      <c r="B15">
+        <v>450301014042</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1017,7 +1014,7 @@
         <v>0.2</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1025,7 +1022,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1037,7 +1034,7 @@
         <v>0.7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1057,35 +1054,35 @@
         <v>0.4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1097,15 +1094,15 @@
         <v>0.4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1117,15 +1114,15 @@
         <v>0.2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1137,7 +1134,7 @@
         <v>1.68</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1157,12 +1154,12 @@
         <v>3.58</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1177,15 +1174,15 @@
         <v>6.54</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1197,15 +1194,15 @@
         <v>1.05</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1217,15 +1214,15 @@
         <v>0.91</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1237,15 +1234,15 @@
         <v>2.15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1257,15 +1254,15 @@
         <v>0.13</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>9</v>
@@ -1277,7 +1274,7 @@
         <v>66.510000000000005</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1285,11 +1282,11 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <f>SUM(E2:E29)</f>
-        <v>177.01500000000004</v>
+        <v>178.36500000000004</v>
       </c>
     </row>
   </sheetData>

--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66033065-B9D6-4C7D-A5E8-88357E117D06}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CAB2CA-DE1F-492A-B2A3-BFFC9FFA381E}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Individual Cost</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
     <t>https://store-usa.arduino.cc/products/arduino-nano?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=US-Pmax&amp;gad_source=1&amp;gclid=CjwKCAjw7pO_BhAlEiwA4pMQvGgjSAL_aiPDuQtjDtxsbhZPY6NtgwMyrIq1obT8kDad0uOfvd-_6xoCrvUQAvD_BwE</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>L314ED American Opto Plus LED | Optoelectronics | DigiKey Marketplace</t>
   </si>
   <si>
-    <t>Chip Resistor - Surface Mount | Electronic Components Distributor DigiKey</t>
-  </si>
-  <si>
     <t>ERJ-8BSJR10V Panasonic Electronic Components | Resistors | DigiKey</t>
   </si>
   <si>
@@ -284,9 +278,6 @@
     <t>B3B-XH-A</t>
   </si>
   <si>
-    <t>RES SMD (1k, 2K, 4.7k) OHM 1% 1/4W 1206</t>
-  </si>
-  <si>
     <t>Schottky Diode</t>
   </si>
   <si>
@@ -300,6 +291,33 @@
   </si>
   <si>
     <t>SD1206T020S1R0</t>
+  </si>
+  <si>
+    <t>Vendor 1</t>
+  </si>
+  <si>
+    <t>RES SMD (1k) OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>RES SMD (2K) OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>RES SMD (4.7k) OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/bourns-inc/CR1206-FX-1001ELF/2562677</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/bourns-inc/CR1206-FX-2001ELF/2562846</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/bourns-inc/CR1206-JW-472ELF/3785627</t>
+  </si>
+  <si>
+    <t>Vendor 2</t>
+  </si>
+  <si>
+    <t>Vendor 3</t>
   </si>
 </sst>
 </file>
@@ -344,9 +362,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -686,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
@@ -694,599 +718,647 @@
     <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.453125" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>24.9</v>
-      </c>
-      <c r="E2">
-        <v>24.9</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5.2450000000000001</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5.2450000000000001</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>12.67</v>
+      </c>
+      <c r="E8" s="2">
+        <v>12.67</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8.23</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8.23</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2">
+        <v>450301014042</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="2">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="2">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="2">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.68</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3.58</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3.58</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>6.54</v>
+      </c>
+      <c r="E26" s="2">
+        <v>6.54</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="153" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2.5</v>
-      </c>
-      <c r="E3">
-        <v>2.5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1.4</v>
-      </c>
-      <c r="E4">
-        <v>1.4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>5.2450000000000001</v>
-      </c>
-      <c r="E6">
-        <v>5.2450000000000001</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="2">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>12.67</v>
-      </c>
-      <c r="E8">
-        <v>12.67</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>4.5</v>
-      </c>
-      <c r="E9">
-        <v>4.5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>13.5</v>
-      </c>
-      <c r="E10">
-        <v>13.5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="E11">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E12">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>8.23</v>
-      </c>
-      <c r="E13">
-        <v>8.23</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15">
-        <v>450301014042</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
-      <c r="E16">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
-      <c r="E17">
-        <v>0.7</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.4</v>
-      </c>
-      <c r="E18">
-        <v>0.4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.3</v>
-      </c>
-      <c r="E19">
-        <v>0.3</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.4</v>
-      </c>
-      <c r="E20">
-        <v>0.4</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0.2</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>0.42</v>
-      </c>
-      <c r="E22">
-        <v>1.68</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>3.58</v>
-      </c>
-      <c r="E23">
-        <v>3.58</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>6.54</v>
-      </c>
-      <c r="E24">
-        <v>6.54</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1.05</v>
-      </c>
-      <c r="E25">
-        <v>1.05</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0.91</v>
-      </c>
-      <c r="E26">
-        <v>0.91</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="D31" s="2">
+        <v>7.39</v>
+      </c>
+      <c r="E31" s="2">
+        <v>66.510000000000005</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>2.15</v>
-      </c>
-      <c r="E27">
-        <v>2.15</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0.13</v>
-      </c>
-      <c r="E28">
-        <v>0.13</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29">
-        <v>9</v>
-      </c>
-      <c r="D29">
-        <v>7.39</v>
-      </c>
-      <c r="E29">
-        <v>66.510000000000005</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B31">
-        <f>SUM(E2:E29)</f>
-        <v>178.36500000000004</v>
+      <c r="B33">
+        <f>SUM(E2:E31)</f>
+        <v>179.76500000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1303,23 +1375,25 @@
     <hyperlink ref="F12" r:id="rId10" display="https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/bk-870/3829737" xr:uid="{27F9BEB5-8046-41B8-A401-6B801AA65292}"/>
     <hyperlink ref="F14" r:id="rId11" display="https://www.amazon.com/Gigastone-10-Pack-Surveillance-Security-Action/dp/B0876H387X/ref=asc_df_B0876H387X?mcid=a36b7487c2ef3bf38be475383d962644&amp;hvocijid=8673258576435803325-B0876H387X-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=8673258576435803325&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435181978&amp;psc=1" xr:uid="{3874B344-6752-4D37-A373-3C0F2F6D39FD}"/>
     <hyperlink ref="F16" r:id="rId12" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
-    <hyperlink ref="F17" r:id="rId13" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
-    <hyperlink ref="F18" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
-    <hyperlink ref="F22" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
-    <hyperlink ref="F23" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="F24" r:id="rId17" display="https://www.grainger.com/product/Pipe-PVC-1ABA1" xr:uid="{98BE1843-601E-422A-8251-9162A4C6D813}"/>
-    <hyperlink ref="F25" r:id="rId18" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
-    <hyperlink ref="F26" r:id="rId19" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="F19" r:id="rId13" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
+    <hyperlink ref="F20" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
+    <hyperlink ref="F24" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
+    <hyperlink ref="F25" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
+    <hyperlink ref="F26" r:id="rId17" display="https://www.grainger.com/product/Pipe-PVC-1ABA1" xr:uid="{98BE1843-601E-422A-8251-9162A4C6D813}"/>
+    <hyperlink ref="F27" r:id="rId18" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
+    <hyperlink ref="F28" r:id="rId19" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
     <hyperlink ref="F13" r:id="rId20" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
     <hyperlink ref="F15" r:id="rId21" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="F20" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="F21" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="F22" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="F23" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
     <hyperlink ref="F3" r:id="rId24" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F29" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="F28" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
-    <hyperlink ref="F19" r:id="rId27" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="F31" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F30" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F21" r:id="rId27" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="F18" r:id="rId28" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
+    <hyperlink ref="F17" r:id="rId29" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId28"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amandasark/Documents/GitHub/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{68C7DE68-14CC-422B-B4F0-50A88173269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CAB2CA-DE1F-492A-B2A3-BFFC9FFA381E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531596A0-E754-B549-9EFC-25FD229D78A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28800" yWindow="6120" windowWidth="38400" windowHeight="21600" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -206,9 +206,6 @@
     <t>MIC5239-5.0YS-TR Microchip Technology | Integrated Circuits (ICs) | DigiKey</t>
   </si>
   <si>
-    <t>PVC, Excelon, Pipe - 1ABA1|4312 - Grainger</t>
-  </si>
-  <si>
     <t>PRT-11864 SparkFun Electronics | Connectors, Interconnects | DigiKey</t>
   </si>
   <si>
@@ -318,6 +315,108 @@
   </si>
   <si>
     <t>Vendor 3</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/arduino/A000005/2638989?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20243136172&amp;gbraid=0AAAAADrbLli4_Ap0H678W2amsXvkFFD8z&amp;gclid=EAIaIQobChMI7K31g6HsjQMVtUP_AR30cCLzEAQYBCABEgJLw_D_BwE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/254630577493?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOorV61PA8LrmcVCLmkRxgli-ic749EmEj9uG3olJqtVqK8C26RwUy3g&amp;gQT=2</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/ai-thinker/NF-01-S/16688873?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20228387720&amp;gbraid=0AAAAADrbLlhsJzz1oN02_raHPEOj6KUUd&amp;gclid=EAIaIQobChMI3MDDyaTsjQMVB0f_AR2LmQ9qEAQYASABEgLeCvD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/185777140664?_trkparms=amclksrc%3DITM%26aid%3D1110006%26algo%3DHOMESPLICE.SIM%26ao%3D1%26asc%3D287247%26meid%3D93c1d507459749bc824a3ce37313f90d%26pid%3D101875%26rk%3D3%26rkt%3D4%26sd%3D226422738360%26itm%3D185777140664%26pmt%3D1%26noa%3D0%26pg%3D2332490%26algv%3DSimVIDwebV3WithCPCExpansionEmbeddingSearchQuerySemanticBroadMatchSingularityRecallReplaceKnnV4WithVectorDbNsOptHotPlRecallCIICentroidCoviewCPCAuto%26brand%3DUnbranded&amp;_trksid=p2332490.c101875.m1851&amp;itmprp=cksum%3A18577714066493c1d507459749bc824a3ce37313f90d%7Cenc%3AAQAKAAABgG96wQ16jds4VFcrhy1F3d4mbwZUJI9Fs%252BgdXYAHIzlX2e3YaNh7x%252BEnKA3G%252BCqSl1Xn4McfcWFK1GytmS2qxJ87mtE8Gm3iR1Ja4WBwh0hNHJrJx3Ki5mp04ow4CO7lP%252BooCybZDDU%252BbbSwmg7CbTin%252BBzBzbCYVnbjvyQAHu6--HI4MB7SvJl5IJqlyvomgoLMlgT6qAJzX0SANJhty2f5YzLv2iQRrcjkpB9yWvuQT%252FD11f5slI2e7QWDMHGTFtcZ50wqMvw%252BJ2RmlUxIXEvTh0LqkZAB7va6mk9vTJtc7Drox1ThtDB19WG5bIW2fHfgLY1uzbmW3a%252Fnm3Xq5q2ZFEfZuha4INRc5aLYqwnMqROltXNjasF%252BOJ2XE8eHi%252FOvOstYWuF0B9daNxq2df0CZ%252FJRsrEsp4L2Uu1GspH%252BFMbSl%252BZrFIdsnBOQo%252F2rJWZSFwMfO%252FC%252FTJvfUez7OsduubS7DzjHJkVpk4KK0CMvuoyIlnVJq3LxYcq7By8laA%253D%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01JXJF02RJ2SD81DKBZE32WGPJ</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Analog-Devices-Maxim-Integrated/DS3231M%2b?qs=Bakm8ERcljpd4MQpcnSykw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/223602242983?chn=ps&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=223602242983&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=108461346&amp;gad_source=4&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9zBpIZmq8atlokvhUYT34hx&amp;gclid=EAIaIQobChMIyYbmlabsjQMVBjUIBR1KhTUNEAQYECABEgIh5fD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/183678893844?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoo96aypxc06QE5iWsXKjoF1TpPWEfeebvqknfWjlxNBuI2BkfrFlCE&amp;gQT=2</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Texas-Instruments/INA219BIDR?qs=1WmUhT/VMINyGsXNJcdD5Q%3D%3D&amp;mgh=1&amp;srsltid=AfmBOoqd-dzv1Ku71Z8di0PO6TdgqgR1Ikm_Kgnfg4GoOsD3-cxDgvEY9rI&amp;gQT=2</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/product/INA219/part-details/INA219BIDR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/3942/9658069?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20232005509&amp;gbraid=0AAAAADrbLlgz3wPXjVsym2RZbeDszCWeE&amp;gclid=EAIaIQobChMI9uW-sajsjQMVHkf_AR02EgvQEAQYASABEgLPSfD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/192312930293?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoqR3Oigp1kS_GZXXLiCTeaArw929kUvWVy0fyYHeb0FzpclMz12k3M</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/11855/5271297?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20243136172&amp;gbraid=0AAAAADrbLli4_Ap0H678W2amsXvkFFD8z&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYAiABEgIY4fD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/365610739537?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoporY_55WDnNvV2pejIbeRgMhPaBkQWl3ds383-qDG6cI2P8OGNJXw&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/133891769676?chn=ps&amp;mkevt=1&amp;mkcid=28&amp;google_free_listing_action=view_item&amp;srsltid=AfmBOoq4Q1DZuqzeXULhra-FvrHzA-CnA0tD2iHCO95TTtg9XNd3Ut4sVOs&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
+  </si>
+  <si>
+    <t>https://business.walmart.com/ip/Gigastone-8GB-Micro-SD-Card-FHD-Video-UHS-I-U1-Class-10-Surveillance-Security-Action-Cameras-Drone-Dash-Cams-5-Pack-5x8GB-GS-2IN1C1008GBX5-B/581920075</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Wurth-Elektronik/450301014042?qs=wr8lucFkNMW0uepaR4R%2Fww%3D%3D&amp;mgh=1&amp;utm_id=22019447991&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=22019464944&amp;gbraid=0AAAAADn_wf3z6_iEM3qu9larZZD8yoLEt&amp;gclid=EAIaIQobChMI3veKsazsjQMVJ0X_AR3ueCPcEAQYBCABEgJYf_D_BwE</t>
+  </si>
+  <si>
+    <t>https://www.lvelectronics.com/details/item?itemid=AOP%20L314ED</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Bourns/CR1206-JW-472ELF?qs=RBg%2F0eAeR6ePTxo24FnKCQ%3D%3D&amp;srsltid=AfmBOooI0BZxUChGiFDzQLEhLuv09GUg3OELUwGj7Guj58z84ioEyLb3</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/KOA-Speer/RK73H2BLTD2001F?qs=iGskpj9dRIVPlylmUlAzCg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/YAGEO/SR1206FR-071KL?qs=k2KEx2DUIRRzYfz4yJHffA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Panasonic/ERJ-8BSJR10V?qs=22lEN67Lqx5%2FgSl4VxUkKw%3D%3D&amp;srsltid=AfmBOooKEwa_yowr04QXCpItXYMgX4VUIlqhSA1qXTuBjw-lAJJuWMzI</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/KYOCERA-AVX/SD1206T020S1R0?qs=jCA%252BPfw4LHaOj8Rzt48dmw%3D%3D&amp;srsltid=AfmBOooK-4y-qkyZkCJ0CVkyP6pI_P6NO2sAjvm4oNRPYUhLXUb5OGXf</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/KYOCERA-AVX/TAJA226K006RNJ?qs=QtLZGLLAmDbrbL0%252BYUNp1A%3D%3D&amp;srsltid=AfmBOoqO2qxkp40s2Bs1PVKz6NKZkPq7v1YTTwfPx3_bcOCE7HDtBbIS</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Panasonic/ECE-A1EKS100B?qs=rMMd5vBiahpNSBku%2FPA9KQ%3D%3D&amp;srsltid=AfmBOoqQ4U271ZrVJxuPMHVWnjSZpLGUJXgJG3eSAxUWLyhrYK65hiV8</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/KEMET/C1206S104K5RACAUTO?qs=ds50AKTGxA9C%252BOGFjvBCPg%3D%3D&amp;srsltid=AfmBOoqQltyUeWiBl72NEX0atiJAYoEHcEyVBj5XktYi3QvV_cm_2CP3</t>
+  </si>
+  <si>
+    <t>https://www.microchipdirect.com/product/MIC5239-5.0YS-TR?srsltid=AfmBOoooHyZrKcH0cUS_RsI3J47TFsMUEwNF8PMOiReEIOzKoqm2jaoz</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Microchip-Technology/MIC5239-5.0YS-TR?qs=U6T8BxXiZAVR02O8mv9RNQ%3D%3D&amp;srsltid=AfmBOor-rXidGcHAi74_wFwNnmEqDxdsndW6D2fPEiDv2uNypmXTMkj8</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/1AAZ8?gucid=N:N:PS:Paid:GGL:CSM-2295:Y8ZQJW:20500801:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=21375667808&amp;gclid=EAIaIQobChMI5eGkh7jsjQMV0kf_AR21aSMcEAQYASABEgKqH_D_BwE</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/SparkFun/PRT-11864?qs=WyAARYrbSnbtPvKJK8JtAA%3D%3D&amp;srsltid=AfmBOopZVoTCh0Q9TrkclEOQVO7rJXLEV4z1l6hZuXLxFMZdjxo1mpZc</t>
+  </si>
+  <si>
+    <t>https://www.samtec.com/products/ssa-104-w-t</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/386425796959?_trkparms=amclksrc%3DITM%26aid%3D1110006%26algo%3DHOMESPLICE.SIM%26ao%3D1%26asc%3D20231107084023%26meid%3D211533ac4c1d4eed8ec70164657222e9%26pid%3D101875%26rk%3D4%26rkt%3D4%26sd%3D122175451692%26itm%3D386425796959%26pmt%3D1%26noa%3D0%26pg%3D2332490%26algv%3DSimVIDwebV3WithCPCExpansionEmbeddingSearchQuerySemanticBroadMatchSingularityRecallReplaceKnnV4WithVectorDbNsOptHotPlRecallCIICentroidCoviewCPCAuto%26brand%3DUnbranded&amp;_trksid=p2332490.c101875.m1851&amp;itmprp=cksum%3A386425796959211533ac4c1d4eed8ec70164657222e9%7Cenc%3AAQAKAAABgG96wQ16jds4VFcrhy1F3d4mbwZUJI9Fs%252BgdXYAHIzlX2e3YaNh7x%252BEnKA3G%252BCqSl1Xn4McfcWFK1GytmS2qxJ87mtE8Gm3iR1Ja4WBwh0hNHJrJx3Ki5mp04ow4CO7lP%252BooCybZDDU%252BbbSwmg7CbTin%252BBzBzbCYVnbjvyQAHu6--HI4MB7SvJl5IJqlyvomgoLMlgT6qAJzX0SANJhty2eKde9FsqA60ez%252FPWqEOa9ipUe1xmjin%252BtcAHHA2qx13AHk%252BDBg9BsRRKvPdJYGCWrPWlqcBwJRvWR2rIoxBKYzJJ1gXC9PogBWeGu58ydhll5N4c%252FTyb1ur6goIbi9zWJj3AA8DhGgBUzuc2HX5Cu7jFZs8Cs31vizil42HiOnM%252BNosmlx8dE5ptHULJ2WtbxxdNMmlnQkd1Rw1XNxGoRDniq5TxfdUanSUegG3iNVh2v5pqQUyi2eZMmTgA6W4tgS%252FO%252FR8vjtoicGtJqVKUKhsdx6G%252Bt9ZqhL5WBmbnLGcw%253D%253D%7Campid%3APL_CLK%7Cclp%3A2332490&amp;itmmeta=01JX0567N9MHM61DNDR0TWAKGV</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/135516167050?_skw=B3B-XH-A&amp;itmmeta=01JXJN27KW3SV3ZA95H65390XD&amp;hash=item1f8d649b8a:g:2rIAAOSwhWlnlDUD&amp;itmprp=enc%3AAQAKAAAAwFkggFvd1GGDu0w3yXCmi1cVMih7yC%2FWve52RdwhMAlOgWsL1OoLM4xoBnc%2B7VbJxO7%2Fl5Q2%2B19FN%2Ffcf4Nh7uGxttthvmZ%2BZODMfmWlr3tqV99qA67ltarFMPt0GZ5Q0hGKwVEs3cWQzRsgzIEMfPrKwt%2FXoqS0kqv8N3acTaphgw--%2B1HloQZc3MjBQEeC3t1OszQttaoyVtLG7P0WoB7S3sUOfGn60RdftLEZV%2BMqhhcdr8JYIK2PYQMDH3SJaA%3D%3D%7Ctkp%3ABk9SR5b6iNXsZQ</t>
   </si>
 </sst>
 </file>
@@ -362,13 +461,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -387,10 +495,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -711,19 +815,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.453125" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
+    <col min="6" max="6" width="69.5" customWidth="1"/>
+    <col min="7" max="7" width="76" customWidth="1"/>
+    <col min="8" max="8" width="83.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
@@ -740,16 +844,16 @@
         <v>35</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -760,36 +864,45 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="E2" s="2">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="E3" s="2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -808,8 +921,14 @@
       <c r="F4" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -820,16 +939,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="E5" s="2">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -840,16 +963,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>5.2450000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="E6" s="2">
-        <v>5.2450000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -860,16 +989,22 @@
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E7" s="2">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -880,16 +1015,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>12.67</v>
+        <v>15.2</v>
       </c>
       <c r="E8" s="2">
-        <v>12.67</v>
+        <v>15.2</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -900,16 +1035,22 @@
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="E9" s="2">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G9" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -920,16 +1061,22 @@
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -948,8 +1095,11 @@
       <c r="F11" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G11" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -968,8 +1118,11 @@
       <c r="F12" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G12" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -986,10 +1139,10 @@
         <v>8.23</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1000,16 +1153,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E14" s="2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G14" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1020,16 +1176,19 @@
         <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1048,13 +1207,16 @@
       <c r="F16" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
@@ -1066,15 +1228,18 @@
         <v>0.7</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="2">
         <v>7</v>
@@ -1086,15 +1251,18 @@
         <v>0.7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -1106,10 +1274,13 @@
         <v>0.7</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1120,96 +1291,111 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="E20" s="2">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="E24" s="2">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1228,10 +1414,16 @@
       <c r="F25" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
@@ -1240,16 +1432,16 @@
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>6.54</v>
+        <v>2.9</v>
       </c>
       <c r="E26" s="2">
-        <v>6.54</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2.9</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1260,16 +1452,19 @@
         <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="E27" s="2">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>34</v>
       </c>
@@ -1286,15 +1481,18 @@
         <v>0.91</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="153" customHeight="1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -1306,15 +1504,18 @@
         <v>2.15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -1326,15 +1527,18 @@
         <v>0.13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2">
         <v>9</v>
@@ -1346,19 +1550,19 @@
         <v>66.510000000000005</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33">
         <f>SUM(E2:E31)</f>
-        <v>179.76500000000004</v>
+        <v>185.8</v>
       </c>
     </row>
   </sheetData>
@@ -1379,21 +1583,27 @@
     <hyperlink ref="F20" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
     <hyperlink ref="F24" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
     <hyperlink ref="F25" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="F26" r:id="rId17" display="https://www.grainger.com/product/Pipe-PVC-1ABA1" xr:uid="{98BE1843-601E-422A-8251-9162A4C6D813}"/>
-    <hyperlink ref="F27" r:id="rId18" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
-    <hyperlink ref="F28" r:id="rId19" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
-    <hyperlink ref="F13" r:id="rId20" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
-    <hyperlink ref="F15" r:id="rId21" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="F22" r:id="rId22" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="F23" r:id="rId23" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
-    <hyperlink ref="F3" r:id="rId24" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F31" r:id="rId25" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="F30" r:id="rId26" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
-    <hyperlink ref="F21" r:id="rId27" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
-    <hyperlink ref="F18" r:id="rId28" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
-    <hyperlink ref="F17" r:id="rId29" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
+    <hyperlink ref="F27" r:id="rId17" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
+    <hyperlink ref="F28" r:id="rId18" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="F13" r:id="rId19" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
+    <hyperlink ref="F15" r:id="rId20" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="F3" r:id="rId23" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
+    <hyperlink ref="F31" r:id="rId24" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F30" r:id="rId25" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F21" r:id="rId26" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="F18" r:id="rId27" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
+    <hyperlink ref="F17" r:id="rId28" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
+    <hyperlink ref="G2" r:id="rId29" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
+    <hyperlink ref="H2" r:id="rId30" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
+    <hyperlink ref="G5" r:id="rId31" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
+    <hyperlink ref="H6" r:id="rId32" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
+    <hyperlink ref="G10" r:id="rId33" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
+    <hyperlink ref="G18" r:id="rId34" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
+    <hyperlink ref="G25" r:id="rId35" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId30"/>
+  <pageSetup orientation="portrait" r:id="rId36"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amandasark/Documents/GitHub/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531596A0-E754-B549-9EFC-25FD229D78A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{531596A0-E754-B549-9EFC-25FD229D78A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61724ACB-31B5-4D98-9322-A3F8943EC0FE}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="6120" windowWidth="38400" windowHeight="21600" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -131,12 +131,6 @@
     <t xml:space="preserve"> Schedule 40 Clear Pipe, Non-threaded</t>
   </si>
   <si>
-    <t>PRT-11864</t>
-  </si>
-  <si>
-    <t>Dean's connector</t>
-  </si>
-  <si>
     <t>SSA-104-W-T</t>
   </si>
   <si>
@@ -206,9 +200,6 @@
     <t>MIC5239-5.0YS-TR Microchip Technology | Integrated Circuits (ICs) | DigiKey</t>
   </si>
   <si>
-    <t>PRT-11864 SparkFun Electronics | Connectors, Interconnects | DigiKey</t>
-  </si>
-  <si>
     <t>SSA-104-W-T Samtec Inc. | Connectors, Interconnects | DigiKey</t>
   </si>
   <si>
@@ -407,9 +398,6 @@
     <t>https://www.grainger.com/product/1AAZ8?gucid=N:N:PS:Paid:GGL:CSM-2295:Y8ZQJW:20500801:APZ_1&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=21375667808&amp;gclid=EAIaIQobChMI5eGkh7jsjQMV0kf_AR21aSMcEAQYASABEgKqH_D_BwE</t>
   </si>
   <si>
-    <t>https://www.mouser.com/ProductDetail/SparkFun/PRT-11864?qs=WyAARYrbSnbtPvKJK8JtAA%3D%3D&amp;srsltid=AfmBOopZVoTCh0Q9TrkclEOQVO7rJXLEV4z1l6hZuXLxFMZdjxo1mpZc</t>
-  </si>
-  <si>
     <t>https://www.samtec.com/products/ssa-104-w-t</t>
   </si>
   <si>
@@ -417,6 +405,9 @@
   </si>
   <si>
     <t>https://www.ebay.com/itm/135516167050?_skw=B3B-XH-A&amp;itmmeta=01JXJN27KW3SV3ZA95H65390XD&amp;hash=item1f8d649b8a:g:2rIAAOSwhWlnlDUD&amp;itmprp=enc%3AAQAKAAAAwFkggFvd1GGDu0w3yXCmi1cVMih7yC%2FWve52RdwhMAlOgWsL1OoLM4xoBnc%2B7VbJxO7%2Fl5Q2%2B19FN%2Ffcf4Nh7uGxttthvmZ%2BZODMfmWlr3tqV99qA67ltarFMPt0GZ5Q0hGKwVEs3cWQzRsgzIEMfPrKwt%2FXoqS0kqv8N3acTaphgw--%2B1HloQZc3MjBQEeC3t1OszQttaoyVtLG7P0WoB7S3sUOfGn60RdftLEZV%2BMqhhcdr8JYIK2PYQMDH3SJaA%3D%3D%7Ctkp%3ABk9SR5b6iNXsZQ</t>
+  </si>
+  <si>
+    <t>4 inch</t>
   </si>
 </sst>
 </file>
@@ -461,7 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -471,9 +462,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -495,6 +483,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -814,46 +806,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.5" customWidth="1"/>
+    <col min="6" max="6" width="69.453125" customWidth="1"/>
     <col min="7" max="7" width="76" customWidth="1"/>
-    <col min="8" max="8" width="83.6640625" customWidth="1"/>
+    <col min="8" max="8" width="83.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -870,21 +862,21 @@
         <v>25.7</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -896,13 +888,13 @@
         <v>2.52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="256" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="232" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -919,16 +911,16 @@
         <v>1.4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -945,14 +937,14 @@
         <v>11.96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -969,16 +961,16 @@
         <v>5.26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>99</v>
+        <v>41</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -995,16 +987,16 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>101</v>
+        <v>42</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1021,15 +1013,15 @@
         <v>15.2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1041,16 +1033,16 @@
         <v>5.25</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1067,16 +1059,16 @@
         <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1093,13 +1085,13 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1116,13 +1108,13 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1139,10 +1131,10 @@
         <v>8.23</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1159,13 +1151,13 @@
         <v>3.5</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1182,13 +1174,13 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1205,18 +1197,18 @@
         <v>0.2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
@@ -1228,18 +1220,18 @@
         <v>0.7</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2">
         <v>7</v>
@@ -1251,18 +1243,18 @@
         <v>0.7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -1274,13 +1266,13 @@
         <v>0.7</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1297,18 +1289,18 @@
         <v>0.34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -1320,18 +1312,18 @@
         <v>0.39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -1343,18 +1335,18 @@
         <v>0.41</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -1366,18 +1358,18 @@
         <v>0.26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -1389,13 +1381,13 @@
         <v>1.92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1412,24 +1404,24 @@
         <v>3.58</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
+      <c r="C26" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="D26" s="2">
         <v>2.9</v>
@@ -1437,11 +1429,11 @@
       <c r="E26" s="2">
         <v>2.9</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="F26" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1452,117 +1444,94 @@
         <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
       <c r="E27" s="2">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2">
+        <v>7.39</v>
+      </c>
+      <c r="E30" s="2">
+        <v>66.510000000000005</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <v>2.15</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2.15</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="2">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2">
-        <v>7.39</v>
-      </c>
-      <c r="E31" s="2">
-        <v>66.510000000000005</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33">
-        <f>SUM(E2:E31)</f>
-        <v>185.8</v>
+      <c r="B32">
+        <f>SUM(E2:E30)</f>
+        <v>184.55</v>
       </c>
     </row>
   </sheetData>
@@ -1583,27 +1552,28 @@
     <hyperlink ref="F20" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
     <hyperlink ref="F24" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
     <hyperlink ref="F25" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.digikey.com/en/products/detail/sparkfun-electronics/PRT-11864/6818769?s=N4IgTCBcDaIAoCUAqBaAjGgHANgCwgF0BfIA" xr:uid="{2FC61876-0275-459F-BE77-C7067ECA8C84}"/>
-    <hyperlink ref="F28" r:id="rId18" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
-    <hyperlink ref="F13" r:id="rId19" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
-    <hyperlink ref="F15" r:id="rId20" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
-    <hyperlink ref="F3" r:id="rId23" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F31" r:id="rId24" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="F30" r:id="rId25" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
-    <hyperlink ref="F21" r:id="rId26" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
-    <hyperlink ref="F18" r:id="rId27" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
-    <hyperlink ref="F17" r:id="rId28" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
-    <hyperlink ref="G2" r:id="rId29" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
-    <hyperlink ref="H2" r:id="rId30" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
-    <hyperlink ref="G5" r:id="rId31" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
-    <hyperlink ref="H6" r:id="rId32" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
-    <hyperlink ref="G10" r:id="rId33" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
-    <hyperlink ref="G18" r:id="rId34" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
-    <hyperlink ref="G25" r:id="rId35" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
+    <hyperlink ref="F27" r:id="rId17" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="F13" r:id="rId18" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
+    <hyperlink ref="F15" r:id="rId19" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="F3" r:id="rId22" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
+    <hyperlink ref="F30" r:id="rId23" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F29" r:id="rId24" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F21" r:id="rId25" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="F18" r:id="rId26" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
+    <hyperlink ref="F17" r:id="rId27" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
+    <hyperlink ref="G2" r:id="rId28" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
+    <hyperlink ref="H2" r:id="rId29" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
+    <hyperlink ref="G5" r:id="rId30" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
+    <hyperlink ref="H6" r:id="rId31" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
+    <hyperlink ref="G10" r:id="rId32" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
+    <hyperlink ref="G18" r:id="rId33" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
+    <hyperlink ref="G25" r:id="rId34" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
+    <hyperlink ref="F26" r:id="rId35" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
+    <hyperlink ref="G3" r:id="rId36" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId36"/>
+  <pageSetup orientation="portrait" r:id="rId37"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amandasark/Documents/GitHub/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{531596A0-E754-B549-9EFC-25FD229D78A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61724ACB-31B5-4D98-9322-A3F8943EC0FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15E8E24-54D6-9341-A7D8-1ED05F1AE174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="35000" yWindow="8360" windowWidth="28800" windowHeight="17500" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -185,9 +185,6 @@
     <t>BK-870 MPD (Memory Protection Devices) | Battery Products | DigiKey</t>
   </si>
   <si>
-    <t>Amazon.com: GIGASTONE 8GB 10-Pack Micro SD Card, Full HD Video, Surveillance Security Cam Action Camera Drone, 85MB/s Micro SDHC Class 10 : Electronics</t>
-  </si>
-  <si>
     <t>L314ED American Opto Plus LED | Optoelectronics | DigiKey Marketplace</t>
   </si>
   <si>
@@ -408,6 +405,30 @@
   </si>
   <si>
     <t>4 inch</t>
+  </si>
+  <si>
+    <t>https://www.staples.com/centon-micro-8gb-sdhc-memory-card-uhs1-5-pack-s1-msdhu1-8g-5-b/product_24298979?locupd=y</t>
+  </si>
+  <si>
+    <t>https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Gigastone-10-Pack-Surveillance-Security-Action/dp/B0876H387X/ref=asc_df_B0876H387X?mcid=a36b7487c2ef3bf38be475383d962644&amp;hvocijid=8673258576435803325-B0876H387X-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=8673258576435803325&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435181978&amp;th=1</t>
+  </si>
+  <si>
+    <t>Vendor 4</t>
+  </si>
+  <si>
+    <t>Vendor 5</t>
+  </si>
+  <si>
+    <t>Vendor 6</t>
   </si>
 </sst>
 </file>
@@ -483,10 +504,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -806,20 +823,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.453125" customWidth="1"/>
+    <col min="6" max="6" width="69.5" customWidth="1"/>
     <col min="7" max="7" width="76" customWidth="1"/>
-    <col min="8" max="8" width="83.6328125" customWidth="1"/>
+    <col min="8" max="8" width="83.6640625" customWidth="1"/>
+    <col min="9" max="9" width="62.6640625" customWidth="1"/>
+    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="11" max="11" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -836,16 +856,25 @@
         <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -865,18 +894,18 @@
         <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -888,13 +917,13 @@
         <v>2.52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="232" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="256" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -914,13 +943,13 @@
         <v>39</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -940,11 +969,11 @@
         <v>40</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -964,13 +993,13 @@
         <v>41</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -990,13 +1019,13 @@
         <v>42</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1016,7 +1045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1036,13 +1065,13 @@
         <v>44</v>
       </c>
       <c r="G9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" ht="89.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1062,13 +1091,13 @@
         <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1088,10 +1117,10 @@
         <v>47</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1111,10 +1140,10 @@
         <v>48</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1131,10 +1160,10 @@
         <v>8.23</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1145,19 +1174,31 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3.5</v>
+        <v>8.24</v>
       </c>
       <c r="E14" s="2">
-        <v>3.5</v>
+        <v>8.24</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1174,13 +1215,13 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1197,18 +1238,18 @@
         <v>0.2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
@@ -1220,18 +1261,18 @@
         <v>0.7</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" s="2">
         <v>7</v>
@@ -1243,18 +1284,18 @@
         <v>0.7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
@@ -1266,13 +1307,13 @@
         <v>0.7</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1289,18 +1330,18 @@
         <v>0.34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -1312,18 +1353,18 @@
         <v>0.39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -1335,18 +1376,18 @@
         <v>0.41</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -1358,18 +1399,18 @@
         <v>0.26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -1381,13 +1422,13 @@
         <v>1.92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1404,24 +1445,24 @@
         <v>3.58</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="2">
         <v>2.9</v>
@@ -1430,10 +1471,10 @@
         <v>2.9</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1450,18 +1491,18 @@
         <v>0.91</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -1473,18 +1514,18 @@
         <v>2.15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -1496,18 +1537,18 @@
         <v>0.13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>9</v>
@@ -1519,19 +1560,19 @@
         <v>66.510000000000005</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
         <f>SUM(E2:E30)</f>
-        <v>184.55</v>
+        <v>189.29000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1546,34 +1587,37 @@
     <hyperlink ref="F10" r:id="rId8" display="https://zeeebattery.com/products/zeee-7-4v-60c-1500mah-2s-lipo-battery-deans-plug?variant=43953770299699&amp;country=US&amp;currency=USD&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;gad_source=1&amp;gclid=CjwKCAjw7pO_BhAlEiwA4pMQvJInDAYww1F-RyBS_FKHJZs2q-GgKMjZj0IEfHsjSMYCjfxmAI9laxoCeRQQAvD_BwE" xr:uid="{BB8CB9D1-9310-4C54-A510-64D6DA058543}"/>
     <hyperlink ref="F11" r:id="rId9" display="https://www.digikey.com/en/products/detail/jauch-quartz/CR1025/16399048" xr:uid="{17A29435-522E-4BB5-8364-3BC77FBEB1C4}"/>
     <hyperlink ref="F12" r:id="rId10" display="https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/bk-870/3829737" xr:uid="{27F9BEB5-8046-41B8-A401-6B801AA65292}"/>
-    <hyperlink ref="F14" r:id="rId11" display="https://www.amazon.com/Gigastone-10-Pack-Surveillance-Security-Action/dp/B0876H387X/ref=asc_df_B0876H387X?mcid=a36b7487c2ef3bf38be475383d962644&amp;hvocijid=8673258576435803325-B0876H387X-&amp;hvexpln=73&amp;tag=hyprod-20&amp;linkCode=df0&amp;hvadid=721245378154&amp;hvpos=&amp;hvnetw=g&amp;hvrand=8673258576435803325&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9198699&amp;hvtargid=pla-2281435181978&amp;psc=1" xr:uid="{3874B344-6752-4D37-A373-3C0F2F6D39FD}"/>
-    <hyperlink ref="F16" r:id="rId12" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
-    <hyperlink ref="F19" r:id="rId13" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
-    <hyperlink ref="F20" r:id="rId14" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
-    <hyperlink ref="F24" r:id="rId15" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
-    <hyperlink ref="F25" r:id="rId16" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
-    <hyperlink ref="F27" r:id="rId17" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
-    <hyperlink ref="F13" r:id="rId18" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
-    <hyperlink ref="F15" r:id="rId19" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
-    <hyperlink ref="F22" r:id="rId20" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
-    <hyperlink ref="F3" r:id="rId22" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
-    <hyperlink ref="F30" r:id="rId23" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
-    <hyperlink ref="F29" r:id="rId24" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
-    <hyperlink ref="F21" r:id="rId25" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
-    <hyperlink ref="F18" r:id="rId26" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
-    <hyperlink ref="F17" r:id="rId27" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
-    <hyperlink ref="G2" r:id="rId28" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
-    <hyperlink ref="H2" r:id="rId29" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
-    <hyperlink ref="G5" r:id="rId30" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
-    <hyperlink ref="H6" r:id="rId31" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
-    <hyperlink ref="G10" r:id="rId32" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
-    <hyperlink ref="G18" r:id="rId33" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
-    <hyperlink ref="G25" r:id="rId34" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
-    <hyperlink ref="F26" r:id="rId35" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
-    <hyperlink ref="G3" r:id="rId36" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
+    <hyperlink ref="F16" r:id="rId11" display="https://www.digikey.com/en/products/detail/american-opto-plus-led/L314ED/13677700?s=N4IgTCBcDaIDIGYCMAWAogERAXQL5A" xr:uid="{EB1FB783-CD78-4F2E-ADAE-2EFC2E0C050D}"/>
+    <hyperlink ref="F19" r:id="rId12" xr:uid="{1CE23A94-3355-4CE3-BD99-944097BF2C76}"/>
+    <hyperlink ref="F20" r:id="rId13" display="https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-8BSJR10V/5647718?s=N4IgTCBcDaIKICUBSBaAHAIQMpIQRgAYA1AAgTixIIDo8SB5ACQFkSBWAHQ4FIS8B6MAHU%2BYAgDYQAXQC%2BQA" xr:uid="{435BBBC4-E5AA-4343-9940-0DAF3E021F72}"/>
+    <hyperlink ref="F24" r:id="rId14" display="https://www.digikey.com/en/products/detail/kemet/c1206s104k5racauto/10232834" xr:uid="{CDDFAE49-11BE-4283-9E44-D17951ACE335}"/>
+    <hyperlink ref="F25" r:id="rId15" display="https://www.digikey.com/en/products/detail/microchip-technology/mic5239-5-0ys-tr/2346595" xr:uid="{0FF0C8FA-B521-42B4-9637-4551CDF56AE0}"/>
+    <hyperlink ref="F27" r:id="rId16" display="https://www.digikey.com/en/products/detail/samtec-inc/ssa-104-w-t/1105908" xr:uid="{5CEFEAD0-E765-4C5C-8B17-4D481AAEE74F}"/>
+    <hyperlink ref="F13" r:id="rId17" xr:uid="{98CBDFFF-5BC0-4691-985C-193C55CD2A4F}"/>
+    <hyperlink ref="F15" r:id="rId18" xr:uid="{F40F3420-CF30-4700-92F3-040B50F37E84}"/>
+    <hyperlink ref="F22" r:id="rId19" xr:uid="{CF84383E-32DC-4F7A-8B1F-D5487EDC174E}"/>
+    <hyperlink ref="F23" r:id="rId20" xr:uid="{9AFC6348-0E57-4A67-A197-41D4FD45794D}"/>
+    <hyperlink ref="F3" r:id="rId21" xr:uid="{132AA37F-9E12-44EF-9546-36BDCE2F9F6B}"/>
+    <hyperlink ref="F30" r:id="rId22" xr:uid="{BECD5DE6-8852-4EA8-869E-7E18A46D5C74}"/>
+    <hyperlink ref="F29" r:id="rId23" display="https://www.digikey.com/en/products/detail/jst-sales-america-inc/B3B-XH-A/1651046?gad_source=1&amp;gad_campaignid=20470400566&amp;gbraid=0AAAAADrbLlgCz6Py2S0va5_igHe8YH5kP&amp;gclid=Cj0KCQjwuvrBBhDcARIsAKRrkjelT39dppIYbNMYGQDQKVRAcVAnRo2gDZvSJK6NkGomAkksSe1uUHcaAmLSEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{9BDFB2BD-EFF6-4DEE-BBC3-2D01594D0DB0}"/>
+    <hyperlink ref="F21" r:id="rId24" xr:uid="{4FB5C311-0780-4C35-9E62-7B63EE0B1C7F}"/>
+    <hyperlink ref="F18" r:id="rId25" xr:uid="{11D1FB24-874A-4110-8E22-DCAAF354D69C}"/>
+    <hyperlink ref="F17" r:id="rId26" xr:uid="{403F8739-6F1C-4926-BB52-7995371B2415}"/>
+    <hyperlink ref="G2" r:id="rId27" xr:uid="{BB65F326-57F6-0948-9C05-235DDBF32C5D}"/>
+    <hyperlink ref="H2" r:id="rId28" xr:uid="{85148DE2-C5FC-5645-B5BB-41BB837D9E5E}"/>
+    <hyperlink ref="G5" r:id="rId29" xr:uid="{41DE90D8-7589-0C4B-AD96-FF698779CC02}"/>
+    <hyperlink ref="H6" r:id="rId30" xr:uid="{50526146-D5B4-5C42-928A-1A4E698E0A66}"/>
+    <hyperlink ref="G10" r:id="rId31" display="https://www.ebay.com/itm/374993811392?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1tgCSJr3fRSKT8fAa1Y7Mgw25&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=374993811392&amp;targetid=2321110923741&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923741&amp;abcId=9448486&amp;merchantid=6296724&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh_duznfnFnLJIwhwQSUm0oBU&amp;gclid=EAIaIQobChMI3euy76jsjQMVFDQIBR3Brw42EAQYBSABEgL8OPD_BwE" xr:uid="{5370FA8F-6BA3-0A44-A70A-E9B0471E8594}"/>
+    <hyperlink ref="G18" r:id="rId32" xr:uid="{FAF305DA-B9D2-2244-A13B-6929AB49025C}"/>
+    <hyperlink ref="G25" r:id="rId33" xr:uid="{B99689F2-D490-2042-A4CC-3BA7CD9172AF}"/>
+    <hyperlink ref="F26" r:id="rId34" xr:uid="{1136733B-68A5-4A0B-995C-2A418A5AC777}"/>
+    <hyperlink ref="G3" r:id="rId35" display="https://www.ebay.com/itm/235081679206?chn=ps&amp;var=536091370095&amp;norover=1&amp;mkevt=1&amp;mkrid=711-117182-37290-0&amp;mkcid=2&amp;mkscid=101&amp;itemid=536091370095_235081679206&amp;targetid=2295557532710&amp;device=c&amp;mktype=pla&amp;googleloc=9198699&amp;poi=&amp;campaignid=21400677539&amp;mkgroupid=173029508628&amp;rlsatarget=pla-2295557532710&amp;abcId=9448483&amp;merchantid=734150552&amp;gad_source=1&amp;gad_campaignid=21400677539&amp;gbraid=0AAAAAD_QDh9KZSet77KcrE8f9gL7cL_CG&amp;gclid=EAIaIQobChMIi8KGzaPsjQMVGEf_AR2yNzdrEAQYAyABEgL6F_D_BwE" xr:uid="{AD11255E-848C-4E6B-B235-2E174E495317}"/>
+    <hyperlink ref="F14" r:id="rId36" xr:uid="{DD127622-0F7B-0F49-8123-68EDBFB9D1FD}"/>
+    <hyperlink ref="G14" r:id="rId37" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
+    <hyperlink ref="H14" r:id="rId38" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
+    <hyperlink ref="I14" r:id="rId39" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amandasark/Documents/GitHub/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15E8E24-54D6-9341-A7D8-1ED05F1AE174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35000" yWindow="8360" windowWidth="28800" windowHeight="17500" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>Vendor 6</t>
+  </si>
+  <si>
+    <t>O-Rings</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/41KX35?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=4fc04ad415926f5f238a2b86e9998fb61d882309f92b5d091786e3ee5833c09a&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
   </si>
 </sst>
 </file>
@@ -1564,15 +1570,29 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F31" s="1"/>
+      <c r="A31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <f>SUM(E2:E30)</f>
-        <v>189.29000000000002</v>
+        <f>SUM(E2:E31)</f>
+        <v>193.99</v>
       </c>
     </row>
   </sheetData>

--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amandasark/Documents/GitHub/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF03F03-B2E1-4173-A4FA-07851DC7CB47}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="136">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -435,6 +435,15 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/41KX35?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=4fc04ad415926f5f238a2b86e9998fb61d882309f92b5d091786e3ee5833c09a&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
+  </si>
+  <si>
+    <t>M2 bolt</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Machine-Screws-M2x0-40-Thread-6GY22?</t>
+  </si>
+  <si>
+    <t>M2 nut</t>
   </si>
 </sst>
 </file>
@@ -829,23 +838,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.5" customWidth="1"/>
+    <col min="6" max="6" width="69.453125" customWidth="1"/>
     <col min="7" max="7" width="76" customWidth="1"/>
-    <col min="8" max="8" width="83.6640625" customWidth="1"/>
-    <col min="9" max="9" width="62.6640625" customWidth="1"/>
-    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="8" max="8" width="83.6328125" customWidth="1"/>
+    <col min="9" max="9" width="62.6328125" customWidth="1"/>
+    <col min="10" max="10" width="55.81640625" customWidth="1"/>
     <col min="11" max="11" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -880,7 +889,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -906,7 +915,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
@@ -929,7 +938,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="256" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="232" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -955,7 +964,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -979,7 +988,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1005,7 +1014,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1031,7 +1040,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1051,7 +1060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1077,7 +1086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="89.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1103,7 +1112,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1149,7 +1158,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1169,7 +1178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1204,7 +1213,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1227,7 +1236,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1250,7 +1259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1273,7 +1282,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1342,7 +1351,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>75</v>
       </c>
@@ -1365,7 +1374,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>57</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>60</v>
       </c>
@@ -1411,7 +1420,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>56</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1460,7 +1469,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>77</v>
       </c>
@@ -1480,7 +1489,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1503,7 +1512,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>66</v>
       </c>
@@ -1526,7 +1535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>72</v>
       </c>
@@ -1549,7 +1558,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
@@ -1569,30 +1578,64 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
         <v>4.7</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E33" s="2">
         <v>4.7</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
-        <f>SUM(E2:E31)</f>
-        <v>193.99</v>
+      <c r="B34">
+        <f>SUM(E2:E33)</f>
+        <v>194.15</v>
       </c>
     </row>
   </sheetData>
@@ -1636,8 +1679,9 @@
     <hyperlink ref="G14" r:id="rId37" tooltip="https://www.staples.com/transcend-8gb-microsdhc-memory-card-class-10-ts8gusdhc10/product_IM1LK3226" xr:uid="{CD78FE6E-F962-024D-BECC-56B99B430391}"/>
     <hyperlink ref="H14" r:id="rId38" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
     <hyperlink ref="I14" r:id="rId39" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
+    <hyperlink ref="F32" r:id="rId40" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId40"/>
+  <pageSetup orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF03F03-B2E1-4173-A4FA-07851DC7CB47}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>

--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF03F03-B2E1-4173-A4FA-07851DC7CB47}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628846D0-6C0C-4E5B-93D7-78F84980544D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -1617,7 +1617,7 @@
         <v>131</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2">
         <v>4.7</v>
@@ -1680,8 +1680,9 @@
     <hyperlink ref="H14" r:id="rId38" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
     <hyperlink ref="I14" r:id="rId39" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
     <hyperlink ref="F32" r:id="rId40" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
+    <hyperlink ref="F33" r:id="rId41" xr:uid="{41E3238C-62D5-4262-AE51-CA98814D973D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId41"/>
+  <pageSetup orientation="portrait" r:id="rId42"/>
 </worksheet>
 </file>
--- a/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials/bill_of_materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/bill_of_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628846D0-6C0C-4E5B-93D7-78F84980544D}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{79DF5EF5-95A3-3841-BD8C-059FB5CD78EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45D0E8C9-E13B-4053-A014-8452C893A4B8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -434,9 +434,6 @@
     <t>O-Rings</t>
   </si>
   <si>
-    <t>https://www.grainger.com/product/41KX35?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=4fc04ad415926f5f238a2b86e9998fb61d882309f92b5d091786e3ee5833c09a&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
-  </si>
-  <si>
     <t>M2 bolt</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t>M2 nut</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/O-Ring-Buna-N-41KW27</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2">
@@ -1596,7 +1596,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2">
@@ -1609,7 +1609,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1617,16 +1617,16 @@
         <v>131</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2">
-        <v>4.7</v>
+        <v>0.26</v>
       </c>
       <c r="E33" s="2">
         <v>4.7</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1680,7 +1680,7 @@
     <hyperlink ref="H14" r:id="rId38" tooltip="https://www.cdwg.com/product/transcend-flash-memory-card-8-gb-microsd/3181432?pfm=srh" xr:uid="{F7564EE8-2A81-B244-AEFD-6DA0DF39B5DC}"/>
     <hyperlink ref="I14" r:id="rId39" tooltip="https://www.cdwg.com/product/kingston-industrial-flash-memory-card-8-gb-microsdhc-uhs-i/6669743?pfm=srh" xr:uid="{6EBC3D1F-2E28-7641-90A9-14D8B6437048}"/>
     <hyperlink ref="F32" r:id="rId40" xr:uid="{AFFADB06-346C-4E3A-B07A-37D406DF404C}"/>
-    <hyperlink ref="F33" r:id="rId41" xr:uid="{41E3238C-62D5-4262-AE51-CA98814D973D}"/>
+    <hyperlink ref="F33" r:id="rId41" xr:uid="{FEC8E672-EBAD-4BB2-B83A-4C72E0C96E83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId42"/>
